--- a/Team-Data/2012-13/3-16-2012-13.xlsx
+++ b/Team-Data/2012-13/3-16-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -799,7 +866,7 @@
         <v>16</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -843,46 +910,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
         <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H3" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
         <v>80.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M3" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.354</v>
+        <v>0.35</v>
       </c>
       <c r="O3" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P3" t="n">
         <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R3" t="n">
         <v>8.300000000000001</v>
@@ -894,7 +961,7 @@
         <v>40</v>
       </c>
       <c r="U3" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
@@ -903,7 +970,7 @@
         <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
@@ -912,31 +979,31 @@
         <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
         <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -945,7 +1012,7 @@
         <v>8</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>26</v>
@@ -954,13 +1021,13 @@
         <v>21</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
         <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -978,7 +1045,7 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1115,10 +1182,10 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>13</v>
@@ -1145,7 +1212,7 @@
         <v>23</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS4" t="n">
         <v>20</v>
@@ -1163,7 +1230,7 @@
         <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>0.212</v>
+        <v>0.215</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,7 +1292,7 @@
         <v>34.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
         <v>0.417</v>
@@ -1240,22 +1307,22 @@
         <v>0.338</v>
       </c>
       <c r="O5" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S5" t="n">
         <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U5" t="n">
         <v>19</v>
@@ -1270,7 +1337,7 @@
         <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z5" t="n">
         <v>19.3</v>
@@ -1279,13 +1346,13 @@
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>92.7</v>
+        <v>92.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-10.2</v>
+        <v>-10</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1303,7 +1370,7 @@
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1327,10 +1394,10 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1479,10 +1546,10 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
         <v>19</v>
@@ -1509,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
         <v>14</v>
@@ -1524,10 +1591,10 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1539,7 +1606,7 @@
         <v>16</v>
       </c>
       <c r="BB6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -1571,64 +1638,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
         <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P7" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.757</v>
+        <v>0.76</v>
       </c>
       <c r="R7" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S7" t="n">
-        <v>28.3</v>
+        <v>28.4</v>
       </c>
       <c r="T7" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X7" t="n">
         <v>3.8</v>
@@ -1637,25 +1704,25 @@
         <v>7.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA7" t="n">
         <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC7" t="n">
         <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
         <v>26</v>
@@ -1670,13 +1737,13 @@
         <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>16</v>
       </c>
       <c r="AM7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN7" t="n">
         <v>20</v>
@@ -1688,7 +1755,7 @@
         <v>11</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
@@ -1700,7 +1767,7 @@
         <v>25</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
         <v>6</v>
@@ -1715,13 +1782,13 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
@@ -1867,7 +1934,7 @@
         <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1900,7 +1967,7 @@
         <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2055,7 +2122,7 @@
         <v>29</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2184,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>0.338</v>
+        <v>0.343</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J10" t="n">
-        <v>81.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
         <v>17.3</v>
       </c>
       <c r="N10" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O10" t="n">
         <v>15.9</v>
@@ -2159,19 +2226,19 @@
         <v>0.694</v>
       </c>
       <c r="R10" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
         <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>6.8</v>
@@ -2189,10 +2256,10 @@
         <v>20.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.1</v>
+        <v>-4</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2201,13 +2268,13 @@
         <v>22</v>
       </c>
       <c r="AF10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2216,16 +2283,16 @@
         <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
@@ -2240,10 +2307,10 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
@@ -2258,7 +2325,7 @@
         <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -2267,7 +2334,7 @@
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC10" t="n">
         <v>26</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2386,10 +2453,10 @@
         <v>13</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
@@ -2404,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2434,7 +2501,7 @@
         <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2446,7 +2513,7 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2625,7 +2692,7 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
         <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>0.606</v>
+        <v>0.615</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,10 +2748,10 @@
         <v>35.1</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>7.1</v>
@@ -2699,13 +2766,13 @@
         <v>16.9</v>
       </c>
       <c r="P13" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S13" t="n">
         <v>32.9</v>
@@ -2714,19 +2781,19 @@
         <v>45.8</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
         <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z13" t="n">
         <v>20.2</v>
@@ -2738,16 +2805,16 @@
         <v>94.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13" t="n">
         <v>7</v>
@@ -2756,13 +2823,13 @@
         <v>12</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>15</v>
@@ -2771,10 +2838,10 @@
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
@@ -2783,7 +2850,7 @@
         <v>19</v>
       </c>
       <c r="AR13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
         <v>6</v>
@@ -2804,7 +2871,7 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>30</v>
@@ -2965,7 +3032,7 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
         <v>22</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
@@ -3123,7 +3190,7 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS15" t="n">
         <v>2</v>
@@ -3159,7 +3226,7 @@
         <v>16</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -3209,61 +3276,61 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
         <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.677</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J16" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="N16" t="n">
         <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="R16" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T16" t="n">
         <v>42.6</v>
       </c>
       <c r="U16" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V16" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W16" t="n">
         <v>8.699999999999999</v>
@@ -3281,13 +3348,13 @@
         <v>19.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
@@ -3296,13 +3363,13 @@
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>20</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
@@ -3329,16 +3396,16 @@
         <v>9</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
@@ -3356,7 +3423,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>7.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
@@ -3708,7 +3775,7 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -3836,13 +3903,13 @@
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF19" t="n">
         <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3854,7 +3921,7 @@
         <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3875,10 +3942,10 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4082,22 @@
         <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4057,7 +4124,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4066,7 +4133,7 @@
         <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -4236,13 +4303,13 @@
         <v>17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
         <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>0.385</v>
+        <v>0.375</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,25 +4750,25 @@
         <v>37.1</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="Q24" t="n">
         <v>0.717</v>
@@ -4710,13 +4777,13 @@
         <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
         <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
@@ -4725,25 +4792,25 @@
         <v>7.3</v>
       </c>
       <c r="X24" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y24" t="n">
         <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>21</v>
@@ -4761,19 +4828,19 @@
         <v>14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>15</v>
@@ -4803,19 +4870,19 @@
         <v>19</v>
       </c>
       <c r="AX24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
         <v>25</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E25" t="n">
         <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J25" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L25" t="n">
         <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.324</v>
+        <v>0.325</v>
       </c>
       <c r="O25" t="n">
         <v>14.7</v>
@@ -4895,10 +4962,10 @@
         <v>30</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
         <v>15.5</v>
@@ -4919,31 +4986,31 @@
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.3</v>
+        <v>-6.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG25" t="n">
         <v>27</v>
       </c>
-      <c r="AG25" t="n">
-        <v>28</v>
-      </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK25" t="n">
         <v>22</v>
@@ -4952,7 +5019,7 @@
         <v>27</v>
       </c>
       <c r="AM25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4967,13 +5034,13 @@
         <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
         <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>15</v>
@@ -4985,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
         <v>34</v>
       </c>
       <c r="G26" t="n">
-        <v>0.477</v>
+        <v>0.469</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5047,7 +5114,7 @@
         <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
@@ -5062,13 +5129,13 @@
         <v>0.347</v>
       </c>
       <c r="O26" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P26" t="n">
         <v>21.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.781</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
         <v>11.1</v>
@@ -5083,7 +5150,7 @@
         <v>21.6</v>
       </c>
       <c r="V26" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5101,34 +5168,34 @@
         <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,34 +5207,34 @@
         <v>23</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR26" t="n">
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5179,10 +5246,10 @@
         <v>22</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5298,10 +5365,10 @@
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>13</v>
@@ -5310,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5355,7 +5422,7 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -5393,64 +5460,64 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.761</v>
+        <v>0.758</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J28" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
         <v>0.789</v>
       </c>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="S28" t="n">
         <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W28" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X28" t="n">
         <v>5.2</v>
@@ -5462,16 +5529,16 @@
         <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.5</v>
+        <v>104.2</v>
       </c>
       <c r="AC28" t="n">
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5531,7 +5598,7 @@
         <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5671,10 +5738,10 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>13</v>
@@ -5698,7 +5765,7 @@
         <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5713,7 +5780,7 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>16</v>
@@ -5725,10 +5792,10 @@
         <v>15</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F30" t="n">
         <v>32</v>
       </c>
       <c r="G30" t="n">
-        <v>0.515</v>
+        <v>0.508</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J30" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K30" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
@@ -5787,31 +5854,31 @@
         <v>16.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O30" t="n">
         <v>18.5</v>
       </c>
       <c r="P30" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q30" t="n">
         <v>0.767</v>
       </c>
       <c r="R30" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S30" t="n">
         <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U30" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V30" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
         <v>8.199999999999999</v>
@@ -5823,19 +5890,19 @@
         <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA30" t="n">
         <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5847,25 +5914,25 @@
         <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK30" t="n">
         <v>14</v>
       </c>
-      <c r="AK30" t="n">
-        <v>15</v>
-      </c>
       <c r="AL30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM30" t="n">
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
@@ -5877,10 +5944,10 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5889,7 +5956,7 @@
         <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>12</v>
@@ -5907,7 +5974,7 @@
         <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
@@ -5939,61 +6006,61 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F31" t="n">
         <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>0.354</v>
+        <v>0.344</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L31" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M31" t="n">
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.364</v>
+        <v>0.358</v>
       </c>
       <c r="O31" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
         <v>20.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.737</v>
+        <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T31" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U31" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6008,34 +6075,34 @@
         <v>20.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>92.5</v>
+        <v>92</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AF31" t="n">
         <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH31" t="n">
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6047,7 +6114,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6059,7 +6126,7 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6089,7 +6156,7 @@
         <v>25</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-16-2012-13</t>
+          <t>2013-03-16</t>
         </is>
       </c>
     </row>
